--- a/光伏配储项目/电价数据/2026/承龙开关站.xlsx
+++ b/光伏配储项目/电价数据/2026/承龙开关站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5744199999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7844500000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.64678</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.60521</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.5662</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.56547</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46785</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.43344</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40491</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.41021</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.43554</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39946</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.39216</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42597</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.43003</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.42273</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.43319</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.45439</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.51471</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31205</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.18717</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.20773</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.26301</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.20516</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.16104</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.18699</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.26269</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.23213</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.06022</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.15779</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.23932</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23914</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.24388</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22841</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.18835</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.82833</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.21169</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.4895</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.50503</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28962</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.50548</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.59028</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5657799999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.72946</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.15516</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.42429</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43062</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43601</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6572899999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.88712</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.49562</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.22288</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.31823</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.09042</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.15166</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.30239</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.42416</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4638</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7066</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.75798</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.26061</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.0533</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.87188</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.7951900000000001</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75524</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51476</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47832</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46561</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.4247</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70651</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.76887</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8711100000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49355</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51195</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5012300000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50144</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48385</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39869</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46607</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37756</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.34621</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.33834</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.36697</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.39507</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.7826900000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6040099999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.73399</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.42193</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.3776600000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38911</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.51168</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34132</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35648</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34068</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.38649</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.41441</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.5698200000000001</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.84401</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.06654</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.37201</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.5717000000000001</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.9247000000000001</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.87986</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.54775</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.8231499999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.22501</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.04872</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35578</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.40594</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.50024</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58526</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.53895</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5346900000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.86113</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6102799999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76497</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.80488</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.1828</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.51048</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.15809</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8610099999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.22857</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.13194</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.29115</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.06924</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.11662</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.67567</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.0096</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9017999999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.00917</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8978400000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.03204</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.84733</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44955</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.81289</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.83663</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42796</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44329</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37532</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33454</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5066499999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48636</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48468</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36744</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38874</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3627</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42671</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36965</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39488</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36635</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36726</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35125</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.35814</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39393</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47099</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35254</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.21595</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.24235</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.16867</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.5225299999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.47822</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.47377</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.55333</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.56214</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.65489</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.6158400000000001</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.84196</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.55596</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.6816599999999999</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.76644</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.86448</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5248999999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.52504</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7882</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.73639</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.64875</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.63618</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5023500000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.5754900000000001</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4665899999999999</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.50248</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50943</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.57739</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.60995</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.57568</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5947100000000001</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.26093</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.61585</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.68304</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46769</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50827</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.57153</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.69011</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.6728200000000001</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.7818200000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.55849</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.44194</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.5158700000000001</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.6094400000000001</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.70813</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.56602</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.8356</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.68338</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5778799999999999</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.51063</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.64358</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45647</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39719</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34188</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5162</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49414</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44049</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38956</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38806</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33874</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43551</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43263</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.42638</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.62746</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.5303300000000001</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4654700000000001</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3762799999999999</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.71363</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.36953</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.4106</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.60678</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.4958</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.42037</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.48848</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.58074</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49572</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45057</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46179</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47667</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.53843</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.62864</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.48048</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6335700000000001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5197999999999999</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49224</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50213</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42947</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4168</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35937</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37557</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31631</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.41482</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.3872</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36192</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3277</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31835</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31011</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34695</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.32112</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.2755</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14452</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.29449</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.00579</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.25698</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27868</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.23942</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.17141</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.16838</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.24333</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.22607</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21972</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.08273</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.14901</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.12496</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.01061</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35841</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35939</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35299</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.37032</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.45036</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37962</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37812</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4593</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34772</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.33204</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36639</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.46918</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.2535</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.2255</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.11905</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.32762</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.23297</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.28415</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.26774</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.24963</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.23922</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.26324</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28859</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10273</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04354</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01114</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20834</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05033</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19219</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.004849999999999999</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06249</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0607</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.3244</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31338</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3797</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31988</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29729</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39403</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42761</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45541</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41527</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38691</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78524</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86985</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6210599999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33084</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5611799999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77754</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39988</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6218400000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44962</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39944</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44677</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.51149</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.56724</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.66226</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.87722</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46671</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5016700000000001</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.40758</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.72105</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.46936</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.84482</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.37269</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.50692</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28111</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.5209900000000001</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.58817</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.40835</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3097200000000001</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28862</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31365</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.34322</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33668</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9027200000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40752</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.3672</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3878</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.35551</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.3298</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32952</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.29576</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3015</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.23366</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30815</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.35678</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19787</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30567</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30186</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30807</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30399</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.29682</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28868</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25391</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.30032</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27461</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.31606</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42054</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.37025</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.42748</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.27618</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8426399999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.42467</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13082</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6768</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.76689</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.62867</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.42996</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.47993</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.41988</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.39493</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.39414</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.37543</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.39885</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39437</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.34864</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3735</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.37789</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.39441</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38015</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.47636</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.2438</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27745</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.31185</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29754</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.47754</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.08184000000000001</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24847</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14831</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.26793</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27493</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02464</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30092</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26012</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2533</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.27869</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28705</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.29942</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.34393</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.49665</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.38569</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6897300000000001</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.40646</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.28252</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.28864</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.23675</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.24574</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.24915</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.24191</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.24563</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.22545</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26399</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.28138</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.22171</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.22178</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.29027</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.11415</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.24016</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.27669</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.1155</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.26402</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.28717</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.23366</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.16219</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.2173</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.2321</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.2721</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.26517</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23378</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.21448</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.22013</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.20611</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.2065</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26607</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.2144</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.26687</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.21693</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26156</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2783</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.24372</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.19769</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.20473</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.20806</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.20365</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.24644</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.21764</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.30026</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.32048</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.34092</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.36922</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.36317</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42717</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.31079</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.41111</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.37186</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.36271</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31824</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30591</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29872</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.2788</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.27479</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.29848</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.28107</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.26738</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27746</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.22668</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31024</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33331</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.40248</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.36172</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35776</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.34222</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.34345</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.3292</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32844</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35367</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32516</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31712</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31555</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.32145</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.31283</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36309</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.41945</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.1899</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.71012</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.5054999999999999</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48645</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.45443</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.53395</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.45334</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39349</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5830700000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.2693</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.25718</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.42913</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.38972</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.7512300000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.46916</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.39733</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.44009</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.42147</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40904</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.55875</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.45665</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36344</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36384</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35042</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.63995</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47508</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.43908</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.45533</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.43737</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71199</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38427</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.49093</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.4896</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49263</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23022</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35216</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.29043</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.13106</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.26048</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.30258</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.31912</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.26231</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.2528</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.25515</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.25135</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.22874</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.27239</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.29015</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.25108</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.25631</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.26679</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.24678</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.23514</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.27314</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33887</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.31626</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26646</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.30205</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.28538</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31798</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.38175</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.34389</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.32676</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.2748</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.24541</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.33271</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.31063</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.33248</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.14727</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.30124</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.31227</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.31356</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.29914</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31334</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.35491</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.37191</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.41468</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.63993</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.69592</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.24831</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.31751</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.3942</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.34183</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.34893</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.36294</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3409700000000001</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.3174</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.29567</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.24693</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.30702</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.27153</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.30123</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.35559</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.31665</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44346</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.47243</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6595299999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61726</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6517000000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.40512</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8201900000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.6039</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.42826</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.5037900000000001</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42967</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.36616</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33409</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.44569</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.40993</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.49839</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.36218</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35889</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.36147</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.37106</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.39247</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46269</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41736</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.47012</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.5067699999999999</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.53779</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.58677</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41754</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41645</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41874</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6681900000000001</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.41829</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.83084</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39157</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.42744</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.36505</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3449700000000001</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.32808</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.37311</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.37167</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.40476</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42334</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.5445099999999999</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.63378</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.46808</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.5479400000000001</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.50104</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.42741</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.55875</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75395</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60694</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6555</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.4026</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.38933</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.38916</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.38289</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.37358</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41749</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.3722</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39915</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.34169</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.1621</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31696</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34899</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.32379</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33818</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39168</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37219</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34437</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38677</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35561</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.5484199999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42773</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.38711</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.44774</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42376</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.45026</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.2245</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.26476</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.30306</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.3855</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41451</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.31366</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.25146</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.26925</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.27851</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.24921</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.34248</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.28878</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.24644</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.16229</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.15201</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.15081</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.24651</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.14599</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.14373</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.23229</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.23861</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.25852</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.23526</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.23896</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.24266</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.13927</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.24637</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.13869</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.12448</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.26122</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.24084</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.22199</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.11661</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27908</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.27603</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27176</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.25361</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.27701</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.008869999999999999</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30712</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.21241</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.26918</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01909</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.23773</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.26487</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.28816</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25265</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25203</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28467</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25932</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30733</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33754</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.30057</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.28672</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.28145</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.30029</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.25883</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.26827</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.29524</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.24359</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.24349</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.28205</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.26887</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.16787</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.24462</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.24084</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.12674</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.24886</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.25647</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.15235</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.12123</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.12895</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.12894</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.12696</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.12696</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.12815</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.24402</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.11895</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.12696</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.12714</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.23444</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.12131</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.13207</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.08581999999999999</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25726</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.12948</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00376</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00022</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1466</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02186</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01537</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04086</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04826</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02933</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04533</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27591</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03768</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01849</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03602</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20235</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27924</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.13025</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29763</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.3289</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.37437</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31699</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.30481</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5600599999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.50005</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24218</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.25906</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.24534</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.2522</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.24861</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.24259</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.22704</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.14893</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.10436</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.12448</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.13188</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.14789</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.11323</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.15627</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.16385</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.17761</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.13116</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.31016</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.60326</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8697</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.85934</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.1079</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.11608</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.27555</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.27375</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.14379</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.08424</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.28022</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00099</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.0005200000000000001</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.0655</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25456</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2919</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47321</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.36395</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.14408</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.67776</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.58585</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.6207999999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9697899999999999</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.59405</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.73868</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.63836</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8290599999999999</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82728</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.83152</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9286599999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.58361</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6343300000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.59054</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33847</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.48863</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.45781</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.4831</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37021</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.29092</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.2679</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.24922</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.26236</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.24169</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.24524</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.13923</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.26006</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.26944</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.39415</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.38693</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.40749</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.34904</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.40121</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.32985</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30898</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25907</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32671</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31497</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33333</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.33601</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3939</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34309</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.41049</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.57264</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.49741</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.38389</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.37883</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.42197</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33999</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.32408</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.32203</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40161</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.40118</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.37109</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33896</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33747</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33535</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.32194</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.4792</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.70568</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.45922</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.46962</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.48022</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.33623</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.34078</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37701</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33858</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.46407</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41864</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47267</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.82251</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.77038</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.43615</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.4792</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.54884</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.7239099999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.85141</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.47055</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.64738</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.41935</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.41601</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43241</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.38287</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.39817</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.36629</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.36181</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.22329</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34017</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.43514</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35869</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3459100000000001</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33593</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33477</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37391</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39105</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35832</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.4347</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36702</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35582</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.36821</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34178</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41128</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.40229</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50315</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55659</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.93308</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.78362</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.64799</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.7279099999999999</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49109</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5769099999999999</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.57905</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.45637</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.73524</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.71114</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.9557</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.85676</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7676900000000001</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.71839</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.38254</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.43899</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.34463</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34831</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35304</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.31203</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34659</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32697</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32523</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.13934</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.31309</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.34718</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33049</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41013</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.35392</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.48894</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.32086</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.18844</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29175</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.41949</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.44616</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.29649</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35477</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.45128</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5521900000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.44463</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45432</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.51913</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.38828</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3719</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.3882</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35856</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.33217</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35058</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.87715</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.52374</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.47619</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43703</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.4158</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36056</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35403</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3450299999999999</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.35486</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35047</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36237</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36069</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34685</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33968</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3192</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37404</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32505</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.33014</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.40184</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4747</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35069</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.38172</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42871</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.37448</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.38683</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37802</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.37827</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.4274</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.48497</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41327</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37796</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4391</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.40954</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.35134</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37194</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37003</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35726</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3623</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31425</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17595</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14561</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19844</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14318</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04593</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22346</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.25881</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14578</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14358</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2828</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.19018</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22664</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26364</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15383</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.15681</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19772</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.1439</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.28168</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.26998</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.3532</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38605</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39807</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.35887</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.45499</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.36724</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37851</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37656</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38055</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.3909</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46157</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.39487</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37891</v>
       </c>
     </row>
   </sheetData>
